--- a/src/R社サンプルデータ.xlsx
+++ b/src/R社サンプルデータ.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21330" windowHeight="11160" firstSheet="4" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21330" windowHeight="11160" firstSheet="6" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="リンク" sheetId="1" r:id="rId1"/>
@@ -1077,18 +1077,6 @@
     <phoneticPr fontId="10"/>
   </si>
   <si>
-    <t>相模原市南区大野台</t>
-    <phoneticPr fontId="10"/>
-  </si>
-  <si>
-    <t>相模原市中央区緑が丘</t>
-    <phoneticPr fontId="10"/>
-  </si>
-  <si>
-    <t>相模原市南区御園</t>
-    <phoneticPr fontId="10"/>
-  </si>
-  <si>
     <r>
       <t>MG</t>
     </r>
@@ -1128,6 +1116,18 @@
   </si>
   <si>
     <t>請求料金 法定外残業単価</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>相模原市南区</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>相模原市中央区</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>相模原市南区</t>
     <phoneticPr fontId="10"/>
   </si>
 </sst>
@@ -1323,10 +1323,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -19100,11 +19100,11 @@
       <c r="B1" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="D1" s="26" t="s">
-        <v>300</v>
+      <c r="C1" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
@@ -19120,7 +19120,7 @@
       <c r="D2" s="12">
         <v>130375</v>
       </c>
-      <c r="E2" s="27"/>
+      <c r="E2" s="25"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1">
       <c r="A4" s="13" t="s">
@@ -19135,19 +19135,19 @@
       <c r="D4" s="12">
         <v>149956</v>
       </c>
-      <c r="E4" s="27"/>
+      <c r="E4" s="25"/>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1">
       <c r="D5" s="12">
         <v>103458</v>
       </c>
-      <c r="E5" s="27"/>
+      <c r="E5" s="25"/>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1">
       <c r="D6" s="12">
         <v>159033</v>
       </c>
-      <c r="E6" s="27"/>
+      <c r="E6" s="25"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10"/>
@@ -19194,11 +19194,11 @@
       <c r="F1" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
       <c r="J1" s="14" t="s">
         <v>106</v>
       </c>
@@ -19226,11 +19226,11 @@
       <c r="R1" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="S1" s="24" t="s">
+      <c r="S1" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
       <c r="V1" s="14" t="s">
         <v>116</v>
       </c>
@@ -19394,8 +19394,8 @@
       <c r="AD2" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="AE2" s="24"/>
-      <c r="AF2" s="25"/>
+      <c r="AE2" s="26"/>
+      <c r="AF2" s="27"/>
       <c r="AG2" s="14"/>
       <c r="AH2" s="14"/>
       <c r="AI2" s="16"/>
@@ -19506,8 +19506,8 @@
       <c r="AD3" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="AE3" s="24"/>
-      <c r="AF3" s="25"/>
+      <c r="AE3" s="26"/>
+      <c r="AF3" s="27"/>
       <c r="AG3" s="14"/>
       <c r="AH3" s="14"/>
       <c r="AI3" s="16"/>
@@ -19557,6 +19557,9 @@
   </sheetPr>
   <dimension ref="A1:BB2"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col min="18" max="18" width="18.54296875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="15.75" customHeight="1">
       <c r="A1" s="14" t="s">
@@ -21200,7 +21203,7 @@
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="4" max="4" width="33.1796875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.6328125" customWidth="1"/>
+    <col min="18" max="18" width="21.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="15.75" customHeight="1">
@@ -21283,7 +21286,7 @@
         <v>179</v>
       </c>
       <c r="AA1" s="14" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AB1" s="14" t="s">
         <v>181</v>
@@ -21322,7 +21325,7 @@
         <v>192</v>
       </c>
       <c r="AN1" s="14" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AO1" s="14" t="s">
         <v>194</v>
@@ -21378,7 +21381,7 @@
         <v>208</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E2" s="17"/>
       <c r="F2" s="15">
@@ -21536,7 +21539,7 @@
         <v>208</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="E3" s="17"/>
       <c r="F3" s="15">
@@ -21696,7 +21699,7 @@
         <v>208</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E4" s="17"/>
       <c r="F4" s="15">
